--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4.xlsx
@@ -402,7 +402,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -570,6 +570,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -579,7 +582,7 @@
               <c:f>'model4(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -746,6 +749,9 @@
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>9376392.18772012</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
               </c:numCache>
@@ -789,7 +795,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -957,6 +963,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -966,7 +975,7 @@
               <c:f>'model4(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1134,6 +1143,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>13579330.276349539</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>14184787.163745383</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1176,7 +1188,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1344,6 +1356,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1353,7 +1368,7 @@
               <c:f>'model4(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1521,6 +1536,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>4202938.088629419</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>4808394.9760252628</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1542,11 +1560,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="433547904"/>
-        <c:axId val="466712448"/>
+        <c:axId val="78677888"/>
+        <c:axId val="92016640"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="433547904"/>
+        <c:axId val="78677888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1589,14 +1607,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="466712448"/>
+        <c:crossAx val="92016640"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="466712448"/>
+        <c:axId val="92016640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1647,7 +1665,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="433547904"/>
+        <c:crossAx val="78677888"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1808,7 +1826,7 @@
               <c:f>'model4(1)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1976,6 +1994,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-63583.378859762786</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-109430.44453916258</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1990,8 +2011,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="507685888"/>
-        <c:axId val="507683200"/>
+        <c:axId val="528384384"/>
+        <c:axId val="522732672"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2016,7 +2037,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -2184,6 +2205,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2193,7 +2217,7 @@
               <c:f>'model4(1)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>4.7860299999999993</c:v>
                 </c:pt>
@@ -2361,6 +2385,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>4.8240952148437497</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5.0477412109374997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2377,11 +2404,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="474835584"/>
-        <c:axId val="475260416"/>
+        <c:axId val="437243264"/>
+        <c:axId val="447632896"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="474835584"/>
+        <c:axId val="437243264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2424,14 +2451,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="475260416"/>
+        <c:crossAx val="447632896"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="475260416"/>
+        <c:axId val="447632896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2482,12 +2509,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="474835584"/>
+        <c:crossAx val="437243264"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="507683200"/>
+        <c:axId val="522732672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2524,12 +2551,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="507685888"/>
+        <c:crossAx val="528384384"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="507685888"/>
+        <c:axId val="528384384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2538,7 +2565,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="507683200"/>
+        <c:crossAx val="522732672"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2947,7 +2974,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG58"/>
+  <dimension ref="A1:AG59"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -5423,6 +5450,44 @@
         <v>519486.93331861048</v>
       </c>
     </row>
+    <row r="59" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A59" s="14">
+        <v>46022</v>
+      </c>
+      <c r="B59" s="15">
+        <v>5.0477412109374997</v>
+      </c>
+      <c r="C59" s="15">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D59" s="16">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E59" s="16">
+        <v>-109430.44453916258</v>
+      </c>
+      <c r="F59" s="17">
+        <v>-21679.09168997165</v>
+      </c>
+      <c r="G59" s="17">
+        <v>2685531.8486840422</v>
+      </c>
+      <c r="H59" s="17">
+        <v>13555869.78588761</v>
+      </c>
+      <c r="I59" s="17">
+        <v>9376392.18772012</v>
+      </c>
+      <c r="J59" s="17">
+        <v>14184787.163745383</v>
+      </c>
+      <c r="K59" s="17">
+        <v>4808394.9760252628</v>
+      </c>
+      <c r="L59" s="16">
+        <v>628917.3778577731</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4.xlsx
@@ -402,7 +402,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -573,6 +573,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -582,7 +585,7 @@
               <c:f>'model4(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -752,6 +755,9 @@
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>9376392.18772012</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
               </c:numCache>
@@ -795,7 +801,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -966,6 +972,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -975,7 +984,7 @@
               <c:f>'model4(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1146,6 +1155,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>14184787.163745383</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>14524323.361325197</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1188,7 +1200,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1359,6 +1371,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1368,7 +1383,7 @@
               <c:f>'model4(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1539,6 +1554,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>4808394.9760252628</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5147931.173605077</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1560,11 +1578,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="78677888"/>
-        <c:axId val="92016640"/>
+        <c:axId val="409097344"/>
+        <c:axId val="493123840"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="78677888"/>
+        <c:axId val="409097344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1607,14 +1625,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92016640"/>
+        <c:crossAx val="493123840"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="92016640"/>
+        <c:axId val="493123840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1665,7 +1683,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78677888"/>
+        <c:crossAx val="409097344"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1826,7 +1844,7 @@
               <c:f>'model4(1)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1997,6 +2015,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-109430.44453916258</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-129990.80506332006</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2011,8 +2032,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="528384384"/>
-        <c:axId val="522732672"/>
+        <c:axId val="559795200"/>
+        <c:axId val="559792896"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2037,7 +2058,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -2208,6 +2229,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2217,7 +2241,7 @@
               <c:f>'model4(1)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>4.7860299999999993</c:v>
                 </c:pt>
@@ -2388,6 +2412,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>5.0477412109374997</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5.1741728515625001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2404,11 +2431,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="437243264"/>
-        <c:axId val="447632896"/>
+        <c:axId val="559776512"/>
+        <c:axId val="559778048"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="437243264"/>
+        <c:axId val="559776512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2451,14 +2478,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="447632896"/>
+        <c:crossAx val="559778048"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="447632896"/>
+        <c:axId val="559778048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2509,12 +2536,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="437243264"/>
+        <c:crossAx val="559776512"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="522732672"/>
+        <c:axId val="559792896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2551,12 +2578,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528384384"/>
+        <c:crossAx val="559795200"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="528384384"/>
+        <c:axId val="559795200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2565,7 +2592,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="522732672"/>
+        <c:crossAx val="559792896"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2974,7 +3001,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG59"/>
+  <dimension ref="A1:AG60"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -5488,6 +5515,44 @@
         <v>628917.3778577731</v>
       </c>
     </row>
+    <row r="60" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A60" s="14">
+        <v>46052</v>
+      </c>
+      <c r="B60" s="15">
+        <v>5.1741728515625001</v>
+      </c>
+      <c r="C60" s="15">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D60" s="16">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E60" s="16">
+        <v>-129990.80506332006</v>
+      </c>
+      <c r="F60" s="17">
+        <v>-25123.011695302244</v>
+      </c>
+      <c r="G60" s="17">
+        <v>2660408.8369887401</v>
+      </c>
+      <c r="H60" s="17">
+        <v>13765415.178404104</v>
+      </c>
+      <c r="I60" s="17">
+        <v>9376392.18772012</v>
+      </c>
+      <c r="J60" s="17">
+        <v>14524323.361325197</v>
+      </c>
+      <c r="K60" s="17">
+        <v>5147931.173605077</v>
+      </c>
+      <c r="L60" s="16">
+        <v>758908.18292109319</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4.xlsx
@@ -402,7 +402,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -576,6 +576,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -585,7 +588,7 @@
               <c:f>'model4(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -758,6 +761,9 @@
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>9376392.18772012</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
               </c:numCache>
@@ -801,7 +807,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -975,6 +981,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -984,7 +993,7 @@
               <c:f>'model4(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1158,6 +1167,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>14524323.361325197</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>14380272.874829827</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1200,7 +1212,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1374,6 +1386,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1383,7 +1398,7 @@
               <c:f>'model4(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1557,6 +1572,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>5147931.173605077</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>5003880.6871097069</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1578,11 +1596,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="409097344"/>
-        <c:axId val="493123840"/>
+        <c:axId val="77523584"/>
+        <c:axId val="77542528"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="409097344"/>
+        <c:axId val="77523584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1625,14 +1643,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="493123840"/>
+        <c:crossAx val="77542528"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="493123840"/>
+        <c:axId val="77542528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1683,7 +1701,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="409097344"/>
+        <c:crossAx val="77523584"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1844,7 +1862,7 @@
               <c:f>'model4(1)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2018,6 +2036,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-129990.80506332006</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-119930.28329170092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2032,8 +2053,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="559795200"/>
-        <c:axId val="559792896"/>
+        <c:axId val="423729024"/>
+        <c:axId val="397588736"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2058,7 +2079,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -2232,6 +2253,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2241,7 +2265,7 @@
               <c:f>'model4(1)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>4.7860299999999993</c:v>
                 </c:pt>
@@ -2415,6 +2439,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>5.1741728515625001</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>5.1200268554687502</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2431,11 +2458,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="559776512"/>
-        <c:axId val="559778048"/>
+        <c:axId val="396994048"/>
+        <c:axId val="397586816"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="559776512"/>
+        <c:axId val="396994048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2478,14 +2505,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559778048"/>
+        <c:crossAx val="397586816"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="559778048"/>
+        <c:axId val="397586816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2536,12 +2563,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559776512"/>
+        <c:crossAx val="396994048"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="559792896"/>
+        <c:axId val="397588736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2578,12 +2605,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559795200"/>
+        <c:crossAx val="423729024"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="559795200"/>
+        <c:axId val="423729024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2592,7 +2619,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="559792896"/>
+        <c:crossAx val="397588736"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3001,7 +3028,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG60"/>
+  <dimension ref="A1:AG61"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -5553,6 +5580,44 @@
         <v>758908.18292109319</v>
       </c>
     </row>
+    <row r="61" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A61" s="14">
+        <v>46080</v>
+      </c>
+      <c r="B61" s="15">
+        <v>5.1200268554687502</v>
+      </c>
+      <c r="C61" s="15">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D61" s="16">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E61" s="16">
+        <v>-119930.28329170092</v>
+      </c>
+      <c r="F61" s="17">
+        <v>-23423.760592896546</v>
+      </c>
+      <c r="G61" s="17">
+        <v>2636985.0763958436</v>
+      </c>
+      <c r="H61" s="17">
+        <v>13501434.408617033</v>
+      </c>
+      <c r="I61" s="17">
+        <v>9376392.18772012</v>
+      </c>
+      <c r="J61" s="17">
+        <v>14380272.874829827</v>
+      </c>
+      <c r="K61" s="17">
+        <v>5003880.6871097069</v>
+      </c>
+      <c r="L61" s="16">
+        <v>878838.46621279407</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4.xlsx
@@ -402,7 +402,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -579,6 +579,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -588,7 +591,7 @@
               <c:f>'model4(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -764,6 +767,9 @@
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>9376392.18772012</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
               </c:numCache>
@@ -807,7 +813,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -984,6 +990,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -993,7 +1002,7 @@
               <c:f>'model4(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1170,6 +1179,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>14380272.874829827</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>13760930.318866894</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1212,7 +1224,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1389,6 +1401,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1398,7 +1413,7 @@
               <c:f>'model4(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1575,6 +1590,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>5003880.6871097069</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>4384538.1311467737</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1596,11 +1614,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="77523584"/>
-        <c:axId val="77542528"/>
+        <c:axId val="392447104"/>
+        <c:axId val="393921280"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="77523584"/>
+        <c:axId val="392447104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1643,14 +1661,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77542528"/>
+        <c:crossAx val="393921280"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="77542528"/>
+        <c:axId val="393921280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1701,7 +1719,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77523584"/>
+        <c:crossAx val="392447104"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1862,7 +1880,7 @@
               <c:f>'model4(1)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2039,6 +2057,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-119930.28329170092</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-76925.150887958705</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2053,8 +2074,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="423729024"/>
-        <c:axId val="397588736"/>
+        <c:axId val="417479680"/>
+        <c:axId val="417478144"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2079,7 +2100,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -2256,6 +2277,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2265,7 +2289,7 @@
               <c:f>'model4(1)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>4.7860299999999993</c:v>
                 </c:pt>
@@ -2442,6 +2466,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>5.1200268554687502</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>4.8851591796875002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2458,11 +2485,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="396994048"/>
-        <c:axId val="397586816"/>
+        <c:axId val="417355264"/>
+        <c:axId val="417357184"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="396994048"/>
+        <c:axId val="417355264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2505,14 +2532,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="397586816"/>
+        <c:crossAx val="417357184"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="397586816"/>
+        <c:axId val="417357184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2563,12 +2590,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="396994048"/>
+        <c:crossAx val="417355264"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="397588736"/>
+        <c:axId val="417478144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2605,12 +2632,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="423729024"/>
+        <c:crossAx val="417479680"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="423729024"/>
+        <c:axId val="417479680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2619,7 +2646,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="397588736"/>
+        <c:crossAx val="417478144"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3028,7 +3055,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG61"/>
+  <dimension ref="A1:AG62"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -5618,6 +5645,44 @@
         <v>878838.46621279407</v>
       </c>
     </row>
+    <row r="62" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A62" s="14">
+        <v>46112</v>
+      </c>
+      <c r="B62" s="15">
+        <v>4.8851591796875002</v>
+      </c>
+      <c r="C62" s="15">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D62" s="16">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E62" s="16">
+        <v>-76925.150887958705</v>
+      </c>
+      <c r="F62" s="17">
+        <v>-15746.70303637466</v>
+      </c>
+      <c r="G62" s="17">
+        <v>2621238.3733594688</v>
+      </c>
+      <c r="H62" s="17">
+        <v>12805166.701766141</v>
+      </c>
+      <c r="I62" s="17">
+        <v>9376392.18772012</v>
+      </c>
+      <c r="J62" s="17">
+        <v>13760930.318866894</v>
+      </c>
+      <c r="K62" s="17">
+        <v>4384538.1311467737</v>
+      </c>
+      <c r="L62" s="16">
+        <v>955763.61710075277</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4.xlsx
@@ -402,7 +402,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -582,6 +582,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -591,7 +594,7 @@
               <c:f>'model4(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -770,6 +773,9 @@
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>9376392.18772012</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
               </c:numCache>
@@ -813,7 +819,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -993,6 +999,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1002,7 +1011,7 @@
               <c:f>'model4(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1182,6 +1191,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>13760930.318866894</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>15492648.634443415</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1224,7 +1236,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1404,6 +1416,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1413,7 +1428,7 @@
               <c:f>'model4(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1593,6 +1608,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>4384538.1311467737</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>6116256.4467232954</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1614,11 +1632,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="392447104"/>
-        <c:axId val="393921280"/>
+        <c:axId val="401425920"/>
+        <c:axId val="401427456"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="392447104"/>
+        <c:axId val="401425920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1661,14 +1679,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="393921280"/>
+        <c:crossAx val="401427456"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="393921280"/>
+        <c:axId val="401427456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1719,7 +1737,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="392447104"/>
+        <c:crossAx val="401425920"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1880,7 +1898,7 @@
               <c:f>'model4(1)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2060,6 +2078,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-76925.150887958705</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-271948.26049911132</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2074,8 +2095,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="417479680"/>
-        <c:axId val="417478144"/>
+        <c:axId val="532536320"/>
+        <c:axId val="472214528"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2100,7 +2121,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -2280,6 +2301,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2289,7 +2313,7 @@
               <c:f>'model4(1)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>4.7860299999999993</c:v>
                 </c:pt>
@@ -2469,6 +2493,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>4.8851591796875002</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>5.5458081054687502</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2485,11 +2512,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="417355264"/>
-        <c:axId val="417357184"/>
+        <c:axId val="463891840"/>
+        <c:axId val="472212992"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="417355264"/>
+        <c:axId val="463891840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2532,14 +2559,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="417357184"/>
+        <c:crossAx val="472212992"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="417357184"/>
+        <c:axId val="472212992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2590,12 +2617,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="417355264"/>
+        <c:crossAx val="463891840"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="417478144"/>
+        <c:axId val="472214528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2632,12 +2659,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="417479680"/>
+        <c:crossAx val="532536320"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="417479680"/>
+        <c:axId val="532536320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2646,7 +2673,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="417478144"/>
+        <c:crossAx val="472214528"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3055,7 +3082,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG62"/>
+  <dimension ref="A1:AG63"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -5683,6 +5710,44 @@
         <v>955763.61710075277</v>
       </c>
     </row>
+    <row r="63" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A63" s="14">
+        <v>46142</v>
+      </c>
+      <c r="B63" s="15">
+        <v>5.5458081054687502</v>
+      </c>
+      <c r="C63" s="15">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D63" s="16">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E63" s="16">
+        <v>-271948.26049911132</v>
+      </c>
+      <c r="F63" s="17">
+        <v>-49036.723833077041</v>
+      </c>
+      <c r="G63" s="17">
+        <v>2572201.6495263916</v>
+      </c>
+      <c r="H63" s="17">
+        <v>14264936.756843552</v>
+      </c>
+      <c r="I63" s="17">
+        <v>9376392.18772012</v>
+      </c>
+      <c r="J63" s="17">
+        <v>15492648.634443415</v>
+      </c>
+      <c r="K63" s="17">
+        <v>6116256.4467232954</v>
+      </c>
+      <c r="L63" s="16">
+        <v>1227711.877599864</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4.xlsx
@@ -402,7 +402,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -585,6 +585,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -594,7 +597,7 @@
               <c:f>'model4(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -776,6 +779,9 @@
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
                 <c:pt idx="60">
+                  <c:v>9376392.18772012</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
               </c:numCache>
@@ -819,7 +825,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1002,6 +1008,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1011,7 +1020,7 @@
               <c:f>'model4(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1194,6 +1203,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>15492648.634443415</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>16585564.304557247</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1236,7 +1248,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1419,6 +1431,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1428,7 +1443,7 @@
               <c:f>'model4(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1611,6 +1626,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>6116256.4467232954</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>7209172.1168371271</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1632,11 +1650,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="401425920"/>
-        <c:axId val="401427456"/>
+        <c:axId val="94116096"/>
+        <c:axId val="99717504"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="401425920"/>
+        <c:axId val="94116096"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1679,14 +1697,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="401427456"/>
+        <c:crossAx val="99717504"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="401427456"/>
+        <c:axId val="99717504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1737,7 +1755,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="401425920"/>
+        <c:crossAx val="94116096"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1898,7 +1916,7 @@
               <c:f>'model4(1)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2081,6 +2099,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>-271948.26049911132</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-329147.77001413936</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2095,8 +2116,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="532536320"/>
-        <c:axId val="472214528"/>
+        <c:axId val="399839616"/>
+        <c:axId val="399528704"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2121,7 +2142,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -2304,6 +2325,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2313,7 +2337,7 @@
               <c:f>'model4(1)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>4.7860299999999993</c:v>
                 </c:pt>
@@ -2496,6 +2520,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>5.5458081054687502</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>5.970703125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2512,11 +2539,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="463891840"/>
-        <c:axId val="472212992"/>
+        <c:axId val="161229824"/>
+        <c:axId val="390302336"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="463891840"/>
+        <c:axId val="161229824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2559,14 +2586,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="472212992"/>
+        <c:crossAx val="390302336"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="472212992"/>
+        <c:axId val="390302336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2617,12 +2644,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="463891840"/>
+        <c:crossAx val="161229824"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="472214528"/>
+        <c:axId val="399528704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2659,12 +2686,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="532536320"/>
+        <c:crossAx val="399839616"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="532536320"/>
+        <c:axId val="399839616"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2673,7 +2700,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="472214528"/>
+        <c:crossAx val="399528704"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3082,7 +3109,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG63"/>
+  <dimension ref="A1:AG64"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -5748,6 +5775,44 @@
         <v>1227711.877599864</v>
       </c>
     </row>
+    <row r="64" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A64" s="14">
+        <v>46171</v>
+      </c>
+      <c r="B64" s="15">
+        <v>5.970703125</v>
+      </c>
+      <c r="C64" s="15">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D64" s="16">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E64" s="16">
+        <v>-329147.77001413936</v>
+      </c>
+      <c r="F64" s="17">
+        <v>-55127.13714335602</v>
+      </c>
+      <c r="G64" s="17">
+        <v>2517074.5123830358</v>
+      </c>
+      <c r="H64" s="17">
+        <v>15028704.656943243</v>
+      </c>
+      <c r="I64" s="17">
+        <v>9376392.18772012</v>
+      </c>
+      <c r="J64" s="17">
+        <v>16585564.304557247</v>
+      </c>
+      <c r="K64" s="17">
+        <v>7209172.1168371271</v>
+      </c>
+      <c r="L64" s="16">
+        <v>1556859.6476140034</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
